--- a/analysis/debtors/JIM001/reports/JIM001_LPG_Reconciliation_v4.xlsx
+++ b/analysis/debtors/JIM001/reports/JIM001_LPG_Reconciliation_v4.xlsx
@@ -219,6 +219,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude (JIM001 bridge review)</author>
+  </authors>
+  <commentList>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>Month attribution: December 2025 (aggregate exact-sum match, R0.01 variance -- rounding). ERP-ledger invoice-level split points to March 2026 instead but is unconfirmed (mechanical FIFO fill of an assumed month, same pattern as doc 40746's June/July case). ASSERTED, not PROVEN -- no remittance advice exists for JIM001. See JIM001_Exact_Sum_Bridge_Review_2026-09-13.md SS5.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude (JIM001 bridge review)</author>
+  </authors>
+  <commentList>
+    <comment ref="D30" authorId="0" shapeId="0">
+      <text>
+        <t>R0.01 variance (11,666.12 vs 11,666.11), same rounding tolerance treated as exact elsewhere in this sheet (e.g. docs 8420, 41664). ASSERTED via aggregate exact-sum match, not PROVEN -- no remittance advice exists for JIM001. Contradicts the unconfirmed ERP-ledger invoice split (allocation_edges.csv AL-0359-AL-0361) which points to March 2026 instead. See JIM001_Exact_Sum_Bridge_Review_2026-09-13.md SS5.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,9 +602,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
@@ -722,9 +750,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n">
         <v>9000.02</v>
       </c>
@@ -1246,9 +1272,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr"/>
       <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n">
         <v>11406.77</v>
       </c>
@@ -1594,9 +1618,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr"/>
       <c r="D51" s="9" t="inlineStr"/>
-      <c r="E51" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n">
         <v>9756.790000000001</v>
       </c>
@@ -1898,9 +1920,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="9" t="inlineStr"/>
-      <c r="E65" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E65" s="10" t="n"/>
       <c r="F65" s="10" t="n">
         <v>13531.77</v>
       </c>
@@ -2136,9 +2156,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr"/>
       <c r="D76" s="5" t="inlineStr"/>
-      <c r="E76" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E76" s="6" t="n"/>
       <c r="F76" s="6" t="n">
         <v>17111.63</v>
       </c>
@@ -2330,9 +2348,7 @@
       </c>
       <c r="C85" s="8" t="inlineStr"/>
       <c r="D85" s="9" t="inlineStr"/>
-      <c r="E85" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E85" s="10" t="n"/>
       <c r="F85" s="10" t="n">
         <v>13817.26</v>
       </c>
@@ -2546,9 +2562,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr"/>
       <c r="D95" s="9" t="inlineStr"/>
-      <c r="E95" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E95" s="10" t="n"/>
       <c r="F95" s="10" t="n">
         <v>16442.26</v>
       </c>
@@ -2850,9 +2864,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr"/>
-      <c r="E109" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E109" s="10" t="n"/>
       <c r="F109" s="10" t="n">
         <v>15673.27</v>
       </c>
@@ -3110,9 +3122,7 @@
       </c>
       <c r="C121" s="8" t="inlineStr"/>
       <c r="D121" s="9" t="inlineStr"/>
-      <c r="E121" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E121" s="10" t="n"/>
       <c r="F121" s="10" t="n">
         <v>15119.26</v>
       </c>
@@ -3348,9 +3358,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr"/>
       <c r="D132" s="5" t="inlineStr"/>
-      <c r="E132" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E132" s="6" t="n"/>
       <c r="F132" s="6" t="n">
         <v>14567.24</v>
       </c>
@@ -3564,9 +3572,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr"/>
       <c r="D142" s="5" t="inlineStr"/>
-      <c r="E142" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E142" s="6" t="n"/>
       <c r="F142" s="6" t="n">
         <v>13442.19</v>
       </c>
@@ -3802,9 +3808,7 @@
       </c>
       <c r="C153" s="8" t="inlineStr"/>
       <c r="D153" s="9" t="inlineStr"/>
-      <c r="E153" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E153" s="10" t="n"/>
       <c r="F153" s="10" t="n">
         <v>24482.13</v>
       </c>
@@ -4084,9 +4088,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr"/>
       <c r="D166" s="5" t="inlineStr"/>
-      <c r="E166" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E166" s="6" t="n"/>
       <c r="F166" s="6" t="n">
         <v>13955.98</v>
       </c>
@@ -4322,9 +4324,7 @@
       </c>
       <c r="C177" s="8" t="inlineStr"/>
       <c r="D177" s="9" t="inlineStr"/>
-      <c r="E177" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E177" s="10" t="n"/>
       <c r="F177" s="10" t="n">
         <v>15081.07</v>
       </c>
@@ -4516,9 +4516,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr"/>
       <c r="D186" s="5" t="inlineStr"/>
-      <c r="E186" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E186" s="6" t="n"/>
       <c r="F186" s="6" t="n">
         <v>26331.1</v>
       </c>
@@ -4710,9 +4708,7 @@
       </c>
       <c r="C195" s="8" t="inlineStr"/>
       <c r="D195" s="9" t="inlineStr"/>
-      <c r="E195" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E195" s="10" t="n"/>
       <c r="F195" s="10" t="n">
         <v>21153.33</v>
       </c>
@@ -4772,9 +4768,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr"/>
       <c r="D198" s="5" t="inlineStr"/>
-      <c r="E198" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E198" s="6" t="n"/>
       <c r="F198" s="6" t="n">
         <v>12903.33</v>
       </c>
@@ -4812,9 +4806,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr"/>
       <c r="D200" s="5" t="inlineStr"/>
-      <c r="E200" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E200" s="6" t="n"/>
       <c r="F200" s="6" t="n">
         <v>9903.33</v>
       </c>
@@ -4852,9 +4844,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr"/>
       <c r="D202" s="5" t="inlineStr"/>
-      <c r="E202" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E202" s="6" t="n"/>
       <c r="F202" s="6" t="n">
         <v>4903.33</v>
       </c>
@@ -4892,9 +4882,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr"/>
       <c r="D204" s="5" t="inlineStr"/>
-      <c r="E204" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E204" s="6" t="n"/>
       <c r="F204" s="6" t="n">
         <v>-221.67</v>
       </c>
@@ -5064,9 +5052,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr"/>
       <c r="D212" s="5" t="inlineStr"/>
-      <c r="E212" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E212" s="6" t="n"/>
       <c r="F212" s="6" t="n">
         <v>12296.53</v>
       </c>
@@ -5258,9 +5244,7 @@
       </c>
       <c r="C221" s="8" t="inlineStr"/>
       <c r="D221" s="9" t="inlineStr"/>
-      <c r="E221" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E221" s="10" t="n"/>
       <c r="F221" s="10" t="n">
         <v>9544.08</v>
       </c>
@@ -5496,9 +5480,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr"/>
       <c r="D232" s="5" t="inlineStr"/>
-      <c r="E232" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E232" s="6" t="n"/>
       <c r="F232" s="6" t="n">
         <v>12001.22</v>
       </c>
@@ -5756,9 +5738,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr"/>
       <c r="D244" s="5" t="inlineStr"/>
-      <c r="E244" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E244" s="6" t="n"/>
       <c r="F244" s="6" t="n">
         <v>858.3099999999999</v>
       </c>
@@ -5906,9 +5886,7 @@
       </c>
       <c r="C251" s="8" t="inlineStr"/>
       <c r="D251" s="9" t="inlineStr"/>
-      <c r="E251" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E251" s="10" t="n"/>
       <c r="F251" s="10" t="n">
         <v>8858.26</v>
       </c>
@@ -6254,9 +6232,7 @@
       </c>
       <c r="C267" s="8" t="inlineStr"/>
       <c r="D267" s="9" t="inlineStr"/>
-      <c r="E267" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E267" s="10" t="n"/>
       <c r="F267" s="10" t="n">
         <v>12790.83</v>
       </c>
@@ -6536,9 +6512,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr"/>
       <c r="D280" s="5" t="inlineStr"/>
-      <c r="E280" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E280" s="6" t="n"/>
       <c r="F280" s="6" t="n">
         <v>13038.61</v>
       </c>
@@ -6818,9 +6792,7 @@
       </c>
       <c r="C293" s="8" t="inlineStr"/>
       <c r="D293" s="9" t="inlineStr"/>
-      <c r="E293" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E293" s="10" t="n"/>
       <c r="F293" s="10" t="n">
         <v>13107.95</v>
       </c>
@@ -7078,9 +7050,7 @@
       </c>
       <c r="C305" s="8" t="inlineStr"/>
       <c r="D305" s="9" t="inlineStr"/>
-      <c r="E305" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E305" s="10" t="n"/>
       <c r="F305" s="10" t="n">
         <v>16557.15</v>
       </c>
@@ -7250,9 +7220,7 @@
       </c>
       <c r="C313" s="8" t="inlineStr"/>
       <c r="D313" s="9" t="inlineStr"/>
-      <c r="E313" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E313" s="10" t="n"/>
       <c r="F313" s="10" t="n">
         <v>16796.63</v>
       </c>
@@ -7466,9 +7434,7 @@
       </c>
       <c r="C323" s="8" t="inlineStr"/>
       <c r="D323" s="9" t="inlineStr"/>
-      <c r="E323" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E323" s="10" t="n"/>
       <c r="F323" s="10" t="n">
         <v>16203.91</v>
       </c>
@@ -7638,9 +7604,7 @@
       </c>
       <c r="C331" s="8" t="inlineStr"/>
       <c r="D331" s="9" t="inlineStr"/>
-      <c r="E331" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E331" s="10" t="n"/>
       <c r="F331" s="10" t="n">
         <v>28709.91</v>
       </c>
@@ -7876,9 +7840,7 @@
       </c>
       <c r="C342" s="4" t="inlineStr"/>
       <c r="D342" s="5" t="inlineStr"/>
-      <c r="E342" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E342" s="6" t="n"/>
       <c r="F342" s="6" t="n">
         <v>30678.89</v>
       </c>
@@ -8070,9 +8032,7 @@
       </c>
       <c r="C351" s="8" t="inlineStr"/>
       <c r="D351" s="9" t="inlineStr"/>
-      <c r="E351" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E351" s="10" t="n"/>
       <c r="F351" s="10" t="n">
         <v>32906.45</v>
       </c>
@@ -8308,9 +8268,7 @@
       </c>
       <c r="C362" s="4" t="inlineStr"/>
       <c r="D362" s="5" t="inlineStr"/>
-      <c r="E362" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E362" s="6" t="n"/>
       <c r="F362" s="6" t="n">
         <v>33669.38</v>
       </c>
@@ -8502,9 +8460,7 @@
       </c>
       <c r="C371" s="8" t="inlineStr"/>
       <c r="D371" s="9" t="inlineStr"/>
-      <c r="E371" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E371" s="10" t="n"/>
       <c r="F371" s="10" t="n">
         <v>49773.14</v>
       </c>
@@ -8652,9 +8608,7 @@
       </c>
       <c r="C378" s="4" t="inlineStr"/>
       <c r="D378" s="5" t="inlineStr"/>
-      <c r="E378" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E378" s="6" t="n"/>
       <c r="F378" s="6" t="n">
         <v>49666.76</v>
       </c>
@@ -8912,9 +8866,7 @@
       </c>
       <c r="C390" s="4" t="inlineStr"/>
       <c r="D390" s="5" t="inlineStr"/>
-      <c r="E390" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E390" s="6" t="n"/>
       <c r="F390" s="6" t="n">
         <v>53282.99</v>
       </c>
@@ -9062,9 +9014,7 @@
       </c>
       <c r="C397" s="8" t="inlineStr"/>
       <c r="D397" s="9" t="inlineStr"/>
-      <c r="E397" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E397" s="10" t="n"/>
       <c r="F397" s="10" t="n">
         <v>52719.78</v>
       </c>
@@ -9190,9 +9140,7 @@
       </c>
       <c r="C403" s="8" t="inlineStr"/>
       <c r="D403" s="9" t="inlineStr"/>
-      <c r="E403" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E403" s="10" t="n"/>
       <c r="F403" s="10" t="n">
         <v>49289.07</v>
       </c>
@@ -9428,9 +9376,7 @@
       </c>
       <c r="C414" s="4" t="inlineStr"/>
       <c r="D414" s="5" t="inlineStr"/>
-      <c r="E414" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E414" s="6" t="n"/>
       <c r="F414" s="6" t="n">
         <v>49494.29</v>
       </c>
@@ -9622,9 +9568,7 @@
       </c>
       <c r="C423" s="8" t="inlineStr"/>
       <c r="D423" s="9" t="inlineStr"/>
-      <c r="E423" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E423" s="10" t="n"/>
       <c r="F423" s="10" t="n">
         <v>53471.03</v>
       </c>
@@ -9750,9 +9694,7 @@
       </c>
       <c r="C429" s="8" t="inlineStr"/>
       <c r="D429" s="9" t="inlineStr"/>
-      <c r="E429" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E429" s="10" t="n"/>
       <c r="F429" s="10" t="n">
         <v>53980.79</v>
       </c>
@@ -9856,9 +9798,7 @@
       </c>
       <c r="C434" s="4" t="inlineStr"/>
       <c r="D434" s="5" t="inlineStr"/>
-      <c r="E434" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E434" s="6" t="n"/>
       <c r="F434" s="6" t="n">
         <v>41139.5</v>
       </c>
@@ -9984,9 +9924,7 @@
       </c>
       <c r="C440" s="4" t="inlineStr"/>
       <c r="D440" s="5" t="inlineStr"/>
-      <c r="E440" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E440" s="6" t="n"/>
       <c r="F440" s="6" t="n">
         <v>45915.32</v>
       </c>
@@ -10090,9 +10028,7 @@
       </c>
       <c r="C445" s="8" t="inlineStr"/>
       <c r="D445" s="9" t="inlineStr"/>
-      <c r="E445" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E445" s="10" t="n"/>
       <c r="F445" s="10" t="n">
         <v>61056.01</v>
       </c>
@@ -10262,9 +10198,7 @@
       </c>
       <c r="C453" s="8" t="inlineStr"/>
       <c r="D453" s="9" t="inlineStr"/>
-      <c r="E453" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E453" s="10" t="n"/>
       <c r="F453" s="10" t="n">
         <v>50672.03</v>
       </c>
@@ -10368,9 +10302,7 @@
       </c>
       <c r="C458" s="4" t="inlineStr"/>
       <c r="D458" s="5" t="inlineStr"/>
-      <c r="E458" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E458" s="6" t="n"/>
       <c r="F458" s="6" t="n">
         <v>64075.09</v>
       </c>
@@ -10518,9 +10450,7 @@
       </c>
       <c r="C465" s="8" t="inlineStr"/>
       <c r="D465" s="9" t="inlineStr"/>
-      <c r="E465" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E465" s="10" t="n"/>
       <c r="F465" s="10" t="n">
         <v>62845.94</v>
       </c>
@@ -10690,9 +10620,7 @@
       </c>
       <c r="C473" s="8" t="inlineStr"/>
       <c r="D473" s="9" t="inlineStr"/>
-      <c r="E473" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E473" s="10" t="n"/>
       <c r="F473" s="10" t="n">
         <v>61559.98</v>
       </c>
@@ -10840,9 +10768,7 @@
       </c>
       <c r="C480" s="4" t="inlineStr"/>
       <c r="D480" s="5" t="inlineStr"/>
-      <c r="E480" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E480" s="6" t="n"/>
       <c r="F480" s="6" t="n">
         <v>55867.88</v>
       </c>
@@ -10990,9 +10916,7 @@
       </c>
       <c r="C487" s="8" t="inlineStr"/>
       <c r="D487" s="9" t="inlineStr"/>
-      <c r="E487" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E487" s="10" t="n"/>
       <c r="F487" s="10" t="n">
         <v>55484.88</v>
       </c>
@@ -11118,9 +11042,7 @@
       </c>
       <c r="C493" s="8" t="inlineStr"/>
       <c r="D493" s="9" t="inlineStr"/>
-      <c r="E493" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E493" s="10" t="n"/>
       <c r="F493" s="10" t="n">
         <v>57172.55</v>
       </c>
@@ -11290,9 +11212,7 @@
       </c>
       <c r="C501" s="8" t="inlineStr"/>
       <c r="D501" s="9" t="inlineStr"/>
-      <c r="E501" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E501" s="10" t="n"/>
       <c r="F501" s="10" t="n">
         <v>48522.37</v>
       </c>
@@ -11462,9 +11382,7 @@
       </c>
       <c r="C509" s="8" t="inlineStr"/>
       <c r="D509" s="9" t="inlineStr"/>
-      <c r="E509" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E509" s="10" t="n"/>
       <c r="F509" s="10" t="n">
         <v>63749.15</v>
       </c>
@@ -11590,9 +11508,7 @@
       </c>
       <c r="C515" s="8" t="inlineStr"/>
       <c r="D515" s="9" t="inlineStr"/>
-      <c r="E515" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E515" s="10" t="n"/>
       <c r="F515" s="10" t="n">
         <v>62064.78</v>
       </c>
@@ -11696,9 +11612,7 @@
       </c>
       <c r="C520" s="4" t="inlineStr"/>
       <c r="D520" s="5" t="inlineStr"/>
-      <c r="E520" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E520" s="6" t="n"/>
       <c r="F520" s="6" t="n">
         <v>74676.91</v>
       </c>
@@ -11824,9 +11738,7 @@
       </c>
       <c r="C526" s="4" t="inlineStr"/>
       <c r="D526" s="5" t="inlineStr"/>
-      <c r="E526" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E526" s="6" t="n"/>
       <c r="F526" s="6" t="n">
         <v>71160.73</v>
       </c>
@@ -11996,9 +11908,7 @@
       </c>
       <c r="C534" s="4" t="inlineStr"/>
       <c r="D534" s="5" t="inlineStr"/>
-      <c r="E534" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E534" s="6" t="n"/>
       <c r="F534" s="6" t="n">
         <v>78312.36</v>
       </c>
@@ -12124,9 +12034,7 @@
       </c>
       <c r="C540" s="4" t="inlineStr"/>
       <c r="D540" s="5" t="inlineStr"/>
-      <c r="E540" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E540" s="6" t="n"/>
       <c r="F540" s="6" t="n">
         <v>79682.50999999999</v>
       </c>
@@ -12318,9 +12226,7 @@
       </c>
       <c r="C549" s="8" t="inlineStr"/>
       <c r="D549" s="9" t="inlineStr"/>
-      <c r="E549" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E549" s="10" t="n"/>
       <c r="F549" s="10" t="n">
         <v>79730.33</v>
       </c>
@@ -12468,9 +12374,7 @@
       </c>
       <c r="C556" s="4" t="inlineStr"/>
       <c r="D556" s="5" t="inlineStr"/>
-      <c r="E556" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E556" s="6" t="n"/>
       <c r="F556" s="6" t="n">
         <v>77279.64999999999</v>
       </c>
@@ -12618,9 +12522,7 @@
       </c>
       <c r="C563" s="8" t="inlineStr"/>
       <c r="D563" s="9" t="inlineStr"/>
-      <c r="E563" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E563" s="10" t="n"/>
       <c r="F563" s="10" t="n">
         <v>72384.36</v>
       </c>
@@ -12812,9 +12714,7 @@
       </c>
       <c r="C572" s="4" t="inlineStr"/>
       <c r="D572" s="5" t="inlineStr"/>
-      <c r="E572" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E572" s="6" t="n"/>
       <c r="F572" s="6" t="n">
         <v>65966.94</v>
       </c>
@@ -12918,9 +12818,7 @@
       </c>
       <c r="C577" s="8" t="inlineStr"/>
       <c r="D577" s="9" t="inlineStr"/>
-      <c r="E577" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E577" s="10" t="n"/>
       <c r="F577" s="10" t="n">
         <v>78491.78999999999</v>
       </c>
@@ -13046,9 +12944,7 @@
       </c>
       <c r="C583" s="8" t="inlineStr"/>
       <c r="D583" s="9" t="inlineStr"/>
-      <c r="E583" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E583" s="10" t="n"/>
       <c r="F583" s="10" t="n">
         <v>75867.3</v>
       </c>
@@ -13196,9 +13092,7 @@
       </c>
       <c r="C590" s="4" t="inlineStr"/>
       <c r="D590" s="5" t="inlineStr"/>
-      <c r="E590" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E590" s="6" t="n"/>
       <c r="F590" s="6" t="n">
         <v>71105.25</v>
       </c>
@@ -13302,9 +13196,7 @@
       </c>
       <c r="C595" s="8" t="inlineStr"/>
       <c r="D595" s="9" t="inlineStr"/>
-      <c r="E595" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E595" s="10" t="n"/>
       <c r="F595" s="10" t="n">
         <v>61875.65</v>
       </c>
@@ -13408,9 +13300,7 @@
       </c>
       <c r="C600" s="4" t="inlineStr"/>
       <c r="D600" s="5" t="inlineStr"/>
-      <c r="E600" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E600" s="6" t="n"/>
       <c r="F600" s="6" t="n">
         <v>73670.89</v>
       </c>
@@ -13536,9 +13426,7 @@
       </c>
       <c r="C606" s="4" t="inlineStr"/>
       <c r="D606" s="5" t="inlineStr"/>
-      <c r="E606" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E606" s="6" t="n"/>
       <c r="F606" s="6" t="n">
         <v>95395.42</v>
       </c>
@@ -13730,9 +13618,7 @@
       </c>
       <c r="C615" s="8" t="inlineStr"/>
       <c r="D615" s="9" t="inlineStr"/>
-      <c r="E615" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E615" s="10" t="n"/>
       <c r="F615" s="10" t="n">
         <v>85583.19</v>
       </c>
@@ -13902,9 +13788,7 @@
       </c>
       <c r="C623" s="8" t="inlineStr"/>
       <c r="D623" s="9" t="inlineStr"/>
-      <c r="E623" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E623" s="10" t="n"/>
       <c r="F623" s="10" t="n">
         <v>79643.61</v>
       </c>
@@ -14074,9 +13958,7 @@
       </c>
       <c r="C631" s="8" t="inlineStr"/>
       <c r="D631" s="9" t="inlineStr"/>
-      <c r="E631" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E631" s="10" t="n"/>
       <c r="F631" s="10" t="n">
         <v>86628.5</v>
       </c>
@@ -14202,9 +14084,7 @@
       </c>
       <c r="C637" s="8" t="inlineStr"/>
       <c r="D637" s="9" t="inlineStr"/>
-      <c r="E637" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E637" s="10" t="n"/>
       <c r="F637" s="10" t="n">
         <v>84450.19</v>
       </c>
@@ -14308,9 +14188,7 @@
       </c>
       <c r="C642" s="4" t="inlineStr"/>
       <c r="D642" s="5" t="inlineStr"/>
-      <c r="E642" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E642" s="6" t="n"/>
       <c r="F642" s="6" t="n">
         <v>97778.06</v>
       </c>
@@ -14458,9 +14336,7 @@
       </c>
       <c r="C649" s="8" t="inlineStr"/>
       <c r="D649" s="9" t="inlineStr"/>
-      <c r="E649" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E649" s="10" t="n"/>
       <c r="F649" s="10" t="n">
         <v>98286.67</v>
       </c>
@@ -14586,9 +14462,7 @@
       </c>
       <c r="C655" s="8" t="inlineStr"/>
       <c r="D655" s="9" t="inlineStr"/>
-      <c r="E655" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E655" s="10" t="n"/>
       <c r="F655" s="10" t="n">
         <v>96588.47</v>
       </c>
@@ -14780,9 +14654,7 @@
       </c>
       <c r="C664" s="4" t="inlineStr"/>
       <c r="D664" s="5" t="inlineStr"/>
-      <c r="E664" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E664" s="6" t="n"/>
       <c r="F664" s="6" t="n">
         <v>98987.49000000001</v>
       </c>
@@ -14908,9 +14780,7 @@
       </c>
       <c r="C670" s="4" t="inlineStr"/>
       <c r="D670" s="5" t="inlineStr"/>
-      <c r="E670" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E670" s="6" t="n"/>
       <c r="F670" s="6" t="n">
         <v>109415.81</v>
       </c>
@@ -15014,9 +14884,7 @@
       </c>
       <c r="C675" s="8" t="inlineStr"/>
       <c r="D675" s="9" t="inlineStr"/>
-      <c r="E675" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E675" s="10" t="n"/>
       <c r="F675" s="10" t="n">
         <v>104397.53</v>
       </c>
@@ -15164,9 +15032,7 @@
       </c>
       <c r="C682" s="4" t="inlineStr"/>
       <c r="D682" s="5" t="inlineStr"/>
-      <c r="E682" s="6" t="n">
-        <v/>
-      </c>
+      <c r="E682" s="6" t="n"/>
       <c r="F682" s="6" t="n">
         <v>120323.88</v>
       </c>
@@ -15270,9 +15136,7 @@
       </c>
       <c r="C687" s="8" t="inlineStr"/>
       <c r="D687" s="9" t="inlineStr"/>
-      <c r="E687" s="10" t="n">
-        <v/>
-      </c>
+      <c r="E687" s="10" t="n"/>
       <c r="F687" s="10" t="n">
         <v>135059.88</v>
       </c>
@@ -15372,7 +15236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17508,17 +17372,45 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="A80" s="7" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>00044555</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Alloc</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>TRANSF</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>STAT 127</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>-11666.12</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>Total Payments Received</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="13">
-        <f>SUM(F4:F79)</f>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="13">
+        <f>SUM(F4:F80)</f>
         <v/>
       </c>
     </row>
@@ -17527,6 +17419,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -17536,7 +17429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -18212,20 +18105,44 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>11666.11</v>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>00044555</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>46178</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>11666.12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Total Matched LPG Sales</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="13">
-        <f>SUM(C4:C29)</f>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="13">
+        <f>SUM(C4:C30)</f>
         <v/>
       </c>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="13">
-        <f>SUM(F4:F29)</f>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="13">
+        <f>SUM(F4:F30)</f>
         <v/>
       </c>
     </row>
@@ -18234,5 +18151,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/analysis/debtors/JIM001/reports/JIM001_LPG_Reconciliation_v4.xlsx
+++ b/analysis/debtors/JIM001/reports/JIM001_LPG_Reconciliation_v4.xlsx
@@ -239,12 +239,12 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>Claude (JIM001 bridge review)</author>
+    <author>Claude</author>
   </authors>
   <commentList>
     <comment ref="D30" authorId="0" shapeId="0">
       <text>
-        <t>R0.01 variance (11,666.12 vs 11,666.11), same rounding tolerance treated as exact elsewhere in this sheet (e.g. docs 8420, 41664). ASSERTED via aggregate exact-sum match, not PROVEN -- no remittance advice exists for JIM001. Contradicts the unconfirmed ERP-ledger invoice split (allocation_edges.csv AL-0359-AL-0361) which points to March 2026 instead. See JIM001_Exact_Sum_Bridge_Review_2026-09-13.md SS5.</t>
+        <t>R0.01 variance (11,666.12 vs 11,666.11), same rounding tolerance treated as exact elsewhere in this sheet (e.g. docs 8420, 41664). CLOSED BY ACCOUNT-OWNER DECISION (2026-09-14): allocated to December 2025 to settle the December-vs-March-2026 dispute ahead of legal handoff. Not independently proven -- the raw ERP ledger (raw/DEBENQ_CURRENT.TXT) shows this payment untagged to any invoice, December included, and the competing March-2026 invoice-level split (allocation_edges.csv AL-0359-AL-0361) is confirmed fictitious (does not exist in the real ERP either). Evidence status: ASSERTED (decision), Tier 3 -- not PROVEN. See JIM001_Exact_Sum_Bridge_Review_2026-09-13.md SS5.</t>
       </text>
     </comment>
   </commentList>
